--- a/缓存数据/concat_area_csm_ly.xlsx
+++ b/缓存数据/concat_area_csm_ly.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51240.59</v>
+        <v>52225.87</v>
       </c>
       <c r="C2" t="n">
-        <v>24011.34</v>
+        <v>25080.36</v>
       </c>
       <c r="D2" t="n">
-        <v>23946.16</v>
+        <v>24984.62</v>
       </c>
       <c r="E2" t="n">
-        <v>65.18000000000001</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>20784.29</v>
+        <v>21840.12</v>
       </c>
       <c r="G2" t="n">
-        <v>3227.05</v>
+        <v>3240.24</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>27229.25</v>
+        <v>27145.51</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52225.87</v>
+        <v>56191.42</v>
       </c>
       <c r="C3" t="n">
-        <v>25080.35999999999</v>
+        <v>23587.13</v>
       </c>
       <c r="D3" t="n">
-        <v>24984.62</v>
+        <v>23544.76</v>
       </c>
       <c r="E3" t="n">
-        <v>95.73999999999999</v>
+        <v>42.37</v>
       </c>
       <c r="F3" t="n">
-        <v>21840.12</v>
+        <v>20396.95</v>
       </c>
       <c r="G3" t="n">
-        <v>3240.24</v>
+        <v>3190.18</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>27145.51</v>
+        <v>32604.29</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56191.42000000001</v>
+        <v>63487.98999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>23587.13000000001</v>
+        <v>27667.94</v>
       </c>
       <c r="D4" t="n">
-        <v>23544.76000000001</v>
+        <v>27551.05000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>42.37</v>
+        <v>116.89</v>
       </c>
       <c r="F4" t="n">
-        <v>20396.95</v>
+        <v>25469.82</v>
       </c>
       <c r="G4" t="n">
-        <v>3190.18</v>
+        <v>2198.119999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>32604.29</v>
+        <v>35820.05</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63487.98999999998</v>
+        <v>60052.98</v>
       </c>
       <c r="C5" t="n">
-        <v>27667.94</v>
+        <v>28540.99</v>
       </c>
       <c r="D5" t="n">
-        <v>27551.05</v>
+        <v>28311.94</v>
       </c>
       <c r="E5" t="n">
-        <v>116.89</v>
+        <v>229.05</v>
       </c>
       <c r="F5" t="n">
-        <v>25469.82</v>
+        <v>26304.05</v>
       </c>
       <c r="G5" t="n">
-        <v>2198.12</v>
+        <v>2236.94</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35820.04999999999</v>
+        <v>31511.99</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60052.98</v>
+        <v>58231.87000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>28540.99</v>
+        <v>27694.60000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>28311.94</v>
+        <v>27461.68</v>
       </c>
       <c r="E6" t="n">
-        <v>229.05</v>
+        <v>232.92</v>
       </c>
       <c r="F6" t="n">
-        <v>26304.05</v>
+        <v>24474.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2236.94</v>
+        <v>3220.559999999999</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>31511.99</v>
+        <v>30537.27</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58231.87000000002</v>
+        <v>58679.98</v>
       </c>
       <c r="C7" t="n">
-        <v>27694.60000000002</v>
+        <v>27086.93</v>
       </c>
       <c r="D7" t="n">
-        <v>27461.68000000001</v>
+        <v>26851.49</v>
       </c>
       <c r="E7" t="n">
-        <v>232.92</v>
+        <v>235.44</v>
       </c>
       <c r="F7" t="n">
-        <v>24474.04</v>
+        <v>24366.69999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3220.559999999999</v>
+        <v>2720.23</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>30537.27</v>
+        <v>31593.05</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58679.98000000001</v>
+        <v>55619.13000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>27086.93</v>
+        <v>27875.31000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>26851.49</v>
+        <v>27645.79000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>235.44</v>
+        <v>229.52</v>
       </c>
       <c r="F8" t="n">
-        <v>24366.7</v>
+        <v>24198.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2720.23</v>
+        <v>3676.53</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>31593.05</v>
+        <v>27743.82000000001</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55619.13000000002</v>
+        <v>57917.53000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>27875.31</v>
+        <v>27643.28</v>
       </c>
       <c r="D9" t="n">
-        <v>27645.79</v>
+        <v>27395.21</v>
       </c>
       <c r="E9" t="n">
-        <v>229.52</v>
+        <v>248.07</v>
       </c>
       <c r="F9" t="n">
-        <v>24198.78</v>
+        <v>24328.12999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>3676.53</v>
+        <v>3315.150000000001</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>27743.82000000001</v>
+        <v>30274.25000000001</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/concat_area_csm_ly.xlsx
+++ b/缓存数据/concat_area_csm_ly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52225.87</v>
+        <v>55562.06000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>25080.36</v>
+        <v>28192.16000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>24984.62</v>
+        <v>28176.40000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>95.73999999999999</v>
+        <v>15.76</v>
       </c>
       <c r="F2" t="n">
-        <v>21840.12</v>
+        <v>24321.56</v>
       </c>
       <c r="G2" t="n">
-        <v>3240.24</v>
+        <v>3870.6</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>27145.51</v>
+        <v>27369.9</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56191.42</v>
+        <v>57798.78000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>23587.13</v>
+        <v>25668.06</v>
       </c>
       <c r="D3" t="n">
-        <v>23544.76</v>
+        <v>25637.13</v>
       </c>
       <c r="E3" t="n">
-        <v>42.37</v>
+        <v>30.93</v>
       </c>
       <c r="F3" t="n">
-        <v>20396.95</v>
+        <v>22095.11</v>
       </c>
       <c r="G3" t="n">
-        <v>3190.18</v>
+        <v>3572.95</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>32604.29</v>
+        <v>32130.72</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63487.98999999999</v>
+        <v>72525.48999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>27667.94</v>
+        <v>24561.75</v>
       </c>
       <c r="D4" t="n">
-        <v>27551.05000000001</v>
+        <v>24539.77</v>
       </c>
       <c r="E4" t="n">
-        <v>116.89</v>
+        <v>21.98</v>
       </c>
       <c r="F4" t="n">
-        <v>25469.82</v>
+        <v>20722.49</v>
       </c>
       <c r="G4" t="n">
-        <v>2198.119999999999</v>
+        <v>3839.259999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35820.05</v>
+        <v>47963.73999999998</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60052.98</v>
+        <v>65576.12999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>28540.99</v>
+        <v>22369.55</v>
       </c>
       <c r="D5" t="n">
-        <v>28311.94</v>
+        <v>22356.49</v>
       </c>
       <c r="E5" t="n">
-        <v>229.05</v>
+        <v>13.06</v>
       </c>
       <c r="F5" t="n">
-        <v>26304.05</v>
+        <v>18513.68</v>
       </c>
       <c r="G5" t="n">
-        <v>2236.94</v>
+        <v>3855.87</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>31511.99</v>
+        <v>43206.57999999999</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58231.87000000001</v>
+        <v>65181.71000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>27694.60000000001</v>
+        <v>24257.85</v>
       </c>
       <c r="D6" t="n">
-        <v>27461.68</v>
+        <v>24255.18</v>
       </c>
       <c r="E6" t="n">
-        <v>232.92</v>
+        <v>2.67</v>
       </c>
       <c r="F6" t="n">
-        <v>24474.04</v>
+        <v>21806.85</v>
       </c>
       <c r="G6" t="n">
-        <v>3220.559999999999</v>
+        <v>2451</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>30537.27</v>
+        <v>40923.86000000001</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58679.98</v>
+        <v>65968.35000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>27086.93</v>
+        <v>23590.74</v>
       </c>
       <c r="D7" t="n">
-        <v>26851.49</v>
+        <v>23571.09</v>
       </c>
       <c r="E7" t="n">
-        <v>235.44</v>
+        <v>19.65</v>
       </c>
       <c r="F7" t="n">
-        <v>24366.69999999999</v>
+        <v>21178.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2720.23</v>
+        <v>2412.07</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>285.71</v>
       </c>
       <c r="I7" t="n">
-        <v>31593.05</v>
+        <v>42377.61000000001</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55619.13000000002</v>
+        <v>61886.71000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>27875.31000000001</v>
+        <v>23920.14000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>27645.79000000001</v>
+        <v>23912.23000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>229.52</v>
+        <v>7.91</v>
       </c>
       <c r="F8" t="n">
-        <v>24198.78</v>
+        <v>21698.28</v>
       </c>
       <c r="G8" t="n">
-        <v>3676.53</v>
+        <v>2221.860000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>285.71</v>
       </c>
       <c r="I8" t="n">
-        <v>27743.82000000001</v>
+        <v>37966.57000000001</v>
       </c>
     </row>
     <row r="9">
@@ -694,31 +694,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57917.53000000001</v>
+        <v>47518.13</v>
       </c>
       <c r="C9" t="n">
-        <v>27643.28</v>
+        <v>21245.09</v>
       </c>
       <c r="D9" t="n">
-        <v>27395.21</v>
+        <v>21218.86</v>
       </c>
       <c r="E9" t="n">
-        <v>248.07</v>
+        <v>26.23</v>
       </c>
       <c r="F9" t="n">
-        <v>24328.12999999999</v>
+        <v>18871.58</v>
       </c>
       <c r="G9" t="n">
-        <v>3315.150000000001</v>
+        <v>2373.51</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>285.71</v>
       </c>
       <c r="I9" t="n">
-        <v>30274.25000000001</v>
+        <v>26273.04</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>